--- a/mock_data/out_data.xlsx
+++ b/mock_data/out_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,80 +454,90 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>C0</t>
+          <t>CPE1_n</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>CPE1_Y0</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>L0</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>chi_square</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>reduced_chi_square</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>chi_square_modulus</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>reduced_chi_square_modulus</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>RMSE_real</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>RMSE_imag</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>RMSE_modulus</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>MAE_real</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>MAE_imag</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>MAE_modulus</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>R2_real</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>R2_imag</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>R2_combined</t>
         </is>
@@ -549,65 +559,71 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>R0-p(C0, R1)</t>
+          <t>L0-R0-p(R1,CPE1)</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>44</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1931821714289376</v>
+        <v>0.6439620729388514</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03130514749499579</v>
+        <v>1.046374575928621</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0587451089443216</v>
+        <v>2.166831949288173e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003861504629838782</v>
+        <v>0.0284832539501964</v>
       </c>
       <c r="L2" t="n">
-        <v>4.542946623339744e-05</v>
+        <v>0.0895293401474513</v>
       </c>
       <c r="M2" t="n">
-        <v>1.984580431203624</v>
+        <v>0.0001090904895381167</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02334800507298381</v>
+        <v>1.314343247447189e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>0.003744478791459681</v>
+        <v>0.02287806504861482</v>
       </c>
       <c r="P2" t="n">
-        <v>0.008587220006514389</v>
+        <v>0.0002756393379351183</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.009368109140054481</v>
+        <v>0.001046640023047193</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00311165381506181</v>
+        <v>0.001176381727943886</v>
       </c>
       <c r="S2" t="n">
-        <v>0.005861928621495548</v>
+        <v>0.001574588615380052</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007285107345083544</v>
+        <v>0.0007130709186039013</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9734256449839093</v>
+        <v>0.0007337760303210858</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6034203113362351</v>
+        <v>0.001124797094534909</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9412129295624737</v>
+        <v>0.997923773842279</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.9925574488436796</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.9983392198359712</v>
       </c>
     </row>
     <row r="3">
@@ -626,65 +642,71 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>R0-p(C0, R1)</t>
+          <t>L0-R0-p(R1,CPE1)</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>44</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1064222544448051</v>
+        <v>0.6638836484759719</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02924187502645252</v>
+        <v>0.7096063454687562</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02052740348149189</v>
+        <v>2.190740042285106e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002099812810850719</v>
+        <v>0.02712761915922235</v>
       </c>
       <c r="L3" t="n">
-        <v>2.470368012765552e-05</v>
+        <v>0.02654201023982932</v>
       </c>
       <c r="M3" t="n">
-        <v>1.716392507787761</v>
+        <v>1.483350950338276e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.02019285303279719</v>
+        <v>1.78716981968467e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001596031397490247</v>
+        <v>0.00669732268807656</v>
       </c>
       <c r="P3" t="n">
-        <v>0.006721287243277941</v>
+        <v>8.069063479610314e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.006908184886670698</v>
+        <v>0.0003205864824586001</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00139050258100035</v>
+        <v>0.0004840966052874089</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003644792536052599</v>
+        <v>0.000580624849611151</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004246735644678062</v>
+        <v>0.0002543216839022982</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9720710414136842</v>
+        <v>0.000329879560251847</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2542676617890509</v>
+        <v>0.000466771301881401</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9439180843040328</v>
+        <v>0.9988731598999983</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.9961315041184527</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.9996038258147845</v>
       </c>
     </row>
     <row r="4">
@@ -703,65 +725,71 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>R0-p(C0, R1)</t>
+          <t>L0-R0-p(R1,CPE1)</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>44</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09286438766381673</v>
+        <v>0.7136145927619593</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02820346907506857</v>
+        <v>0.4563608918237077</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01469659790321822</v>
+        <v>2.191051886226431e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001988257114963343</v>
+        <v>0.02643688161596837</v>
       </c>
       <c r="L4" t="n">
-        <v>2.339126017603933e-05</v>
+        <v>0.01815902939427276</v>
       </c>
       <c r="M4" t="n">
-        <v>1.748999872398019</v>
+        <v>5.934618944594927e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02057646908703552</v>
+        <v>7.150143306740876e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001061385162998802</v>
+        <v>0.003364919950503362</v>
       </c>
       <c r="P4" t="n">
-        <v>0.006637855319263773</v>
+        <v>4.054120422293207e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.006722176857515157</v>
+        <v>0.0002045343067371428</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0009370680392535321</v>
+        <v>0.0003050301962983415</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003211773712585685</v>
+        <v>0.000367256998961556</v>
       </c>
       <c r="T4" t="n">
-        <v>0.003606888457756076</v>
+        <v>0.0001597601204970993</v>
       </c>
       <c r="U4" t="n">
-        <v>0.976616157004656</v>
+        <v>0.0002043501195194126</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1403063098483593</v>
+        <v>0.0002856979086989357</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9384969233162077</v>
+        <v>0.9991316352455262</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.9981845936788436</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.9998164234789899</v>
       </c>
     </row>
     <row r="5">
@@ -780,65 +808,71 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>R0-p(C0, R1)</t>
+          <t>L0-R0-p(R1,CPE1)</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>44</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1645143460279387</v>
+        <v>0.6745084366404235</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02843279701937849</v>
+        <v>0.8233036771673222</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06270801924178714</v>
+        <v>2.189232715341079e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00456830575902529</v>
+        <v>0.02592466725938523</v>
       </c>
       <c r="L5" t="n">
-        <v>5.374477363559165e-05</v>
+        <v>0.09278811417687445</v>
       </c>
       <c r="M5" t="n">
-        <v>2.24221595442374</v>
+        <v>0.0001217150646234802</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02637901122851459</v>
+        <v>1.466446561728678e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004161578684729915</v>
+        <v>0.01537190044692382</v>
       </c>
       <c r="P5" t="n">
-        <v>0.009300881341987975</v>
+        <v>0.0001852036198424557</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01018946175648834</v>
+        <v>0.0008746493187746066</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003207915850865531</v>
+        <v>0.00141465191403489</v>
       </c>
       <c r="S5" t="n">
-        <v>0.006521187784146817</v>
+        <v>0.0016632051793797</v>
       </c>
       <c r="T5" t="n">
-        <v>0.007889618635466458</v>
+        <v>0.0005551794088774149</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9726454166688541</v>
+        <v>0.0006088800211236508</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5848879647128822</v>
+        <v>0.0009223960402058583</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9329231965296364</v>
+        <v>0.9987916804352582</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.9903967927764734</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.998212847847804</v>
       </c>
     </row>
     <row r="6">
@@ -857,65 +891,71 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>R0-p(C0, R1)</t>
+          <t>L0-R0-p(R1,CPE1)</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>44</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1128205246590002</v>
+        <v>0.7123530516573859</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02681232414895221</v>
+        <v>0.5726337162388287</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02117239076141702</v>
+        <v>2.187074195135123e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002108960861027357</v>
+        <v>0.02515619006358801</v>
       </c>
       <c r="L6" t="n">
-        <v>2.481130424738067e-05</v>
+        <v>0.02625112384838284</v>
       </c>
       <c r="M6" t="n">
-        <v>1.9207169627706</v>
+        <v>1.621730846551519e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02259667015024235</v>
+        <v>1.953892586206649e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001488388607662625</v>
+        <v>0.007791675482457162</v>
       </c>
       <c r="P6" t="n">
-        <v>0.006761333301375756</v>
+        <v>9.387560822237544e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.00692321664110785</v>
+        <v>0.0003325279708866992</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001263066493871654</v>
+        <v>0.0005079373396158694</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003696644848049676</v>
+        <v>0.0006071039387107222</v>
       </c>
       <c r="T6" t="n">
-        <v>0.004237368053029347</v>
+        <v>0.0002642393239876355</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9768182623332062</v>
+        <v>0.0003252840282887055</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2711340498806606</v>
+        <v>0.0004702606130132885</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9379001935542461</v>
+        <v>0.9988429032415101</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.995886578138967</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.9995224701722113</v>
       </c>
     </row>
     <row r="7">
@@ -934,65 +974,71 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>R0-p(C0, R1)</t>
+          <t>L0-R0-p(R1,CPE1)</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>44</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1121798569115333</v>
+        <v>0.7246737596294067</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02610561279434866</v>
+        <v>0.5104662923356826</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01352127033835269</v>
+        <v>2.188507443052361e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001996100533288515</v>
+        <v>0.02460468050237551</v>
       </c>
       <c r="L7" t="n">
-        <v>2.348353568574724e-05</v>
+        <v>0.01658153761015271</v>
       </c>
       <c r="M7" t="n">
-        <v>1.940863146033151</v>
+        <v>5.790294729522851e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02283368407097825</v>
+        <v>6.976258710268494e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0009663585122363028</v>
+        <v>0.003709102795067837</v>
       </c>
       <c r="P7" t="n">
-        <v>0.006665738701519214</v>
+        <v>4.468798548274502e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.006735422868024146</v>
+        <v>0.0001871461664109066</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0008437723284323886</v>
+        <v>0.0003107634468319222</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003247603138005611</v>
+        <v>0.0003627638453445377</v>
       </c>
       <c r="T7" t="n">
-        <v>0.003595213557101626</v>
+        <v>0.0001441085348144864</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9770576087166692</v>
+        <v>0.0001773975235749939</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1181671560245157</v>
+        <v>0.000254061724413896</v>
       </c>
       <c r="W7" t="n">
-        <v>0.928806372511233</v>
+        <v>0.9991395532473982</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.9980833202289051</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.9997934813005913</v>
       </c>
     </row>
   </sheetData>
